--- a/Initial_data/2024/C_org.xlsx
+++ b/Initial_data/2024/C_org.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kirill\Desktop\Lab\KNP-analysis\Initial_data\2024\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F18E1E-7310-4C84-8E49-483185CFD5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>Sample</t>
   </si>
@@ -599,95 +606,379 @@
   </si>
   <si>
     <t>LG-17-2-30</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-6</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-7</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-8</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-5</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B2-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B1-4</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-B3-3</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BZ-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-1</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-2</t>
-  </si>
-  <si>
-    <t>ADOM-SLB-BO-3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -710,9 +1001,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -720,17 +1253,61 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1015,16 +1592,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B212"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B192"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="97.1428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1040,7 +1620,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1048,7 +1628,7 @@
         <v>31.55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1056,15 +1636,15 @@
         <v>22.91</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>9.7129999999999992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.713</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1072,7 +1652,7 @@
         <v>25.23</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1080,7 +1660,7 @@
         <v>16.21</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1088,7 +1668,7 @@
         <v>17.72</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1096,7 +1676,7 @@
         <v>13.71</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1104,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1112,7 +1692,7 @@
         <v>11.77</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1120,15 +1700,15 @@
         <v>1.633</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13">
-        <v>9.1739999999999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1136,47 +1716,47 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15">
-        <v>5.9640000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5.964</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.3679999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.368</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
-        <v>2.5720000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.572</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18">
-        <v>3.1520000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.152</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
-        <v>4.1840000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4.184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1184,7 +1764,7 @@
         <v>23.88</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1192,7 +1772,7 @@
         <v>14.26</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1200,7 +1780,7 @@
         <v>14.13</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1208,7 +1788,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1216,31 +1796,31 @@
         <v>1.337</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.9630000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1.963</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
       <c r="B26">
-        <v>2.8610000000000002</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
       <c r="B27">
-        <v>4.1520000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4.152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1248,39 +1828,39 @@
         <v>13.17</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.6389999999999998</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.639</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30">
-        <v>3.2629999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
       <c r="B31">
-        <v>3.9790000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.979</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
       <c r="B32">
-        <v>9.3330000000000002</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.333</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1288,7 +1868,7 @@
         <v>25.65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -1296,7 +1876,7 @@
         <v>22.14</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -1304,7 +1884,7 @@
         <v>22.78</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -1312,7 +1892,7 @@
         <v>26.39</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -1320,7 +1900,7 @@
         <v>11.99</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -1328,23 +1908,23 @@
         <v>12.19</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2">
       <c r="A39" t="s">
         <v>39</v>
       </c>
       <c r="B39">
-        <v>9.1980000000000004</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" t="s">
         <v>40</v>
       </c>
       <c r="B40">
-        <v>9.9350000000000005</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.935</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -1352,7 +1932,7 @@
         <v>12.02</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -1360,7 +1940,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -1368,7 +1948,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -1376,7 +1956,7 @@
         <v>18.97</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -1384,7 +1964,7 @@
         <v>30.88</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -1392,23 +1972,23 @@
         <v>13.81</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2">
       <c r="A47" t="s">
         <v>47</v>
       </c>
       <c r="B47">
-        <v>8.2690000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.269</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>48</v>
       </c>
       <c r="B48">
-        <v>16.809999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>16.81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -1416,7 +1996,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -1424,7 +2004,7 @@
         <v>10.86</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -1432,7 +2012,7 @@
         <v>14.61</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -1440,7 +2020,7 @@
         <v>15.56</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -1448,7 +2028,7 @@
         <v>16.09</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -1456,7 +2036,7 @@
         <v>17.32</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -1464,31 +2044,31 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>56</v>
       </c>
       <c r="B56">
-        <v>8.1940000000000008</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.194</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>57</v>
       </c>
       <c r="B57">
-        <v>8.2690000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.269</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>58</v>
       </c>
       <c r="B58">
-        <v>8.1940000000000008</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.194</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -1496,15 +2076,15 @@
         <v>13.03</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>60</v>
       </c>
       <c r="B60">
-        <v>9.8659999999999997</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.866</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -1512,7 +2092,7 @@
         <v>14.82</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -1520,7 +2100,7 @@
         <v>12.15</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -1528,7 +2108,7 @@
         <v>14.83</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -1536,7 +2116,7 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -1544,7 +2124,7 @@
         <v>13.24</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -1552,7 +2132,7 @@
         <v>14.38</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -1560,7 +2140,7 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -1568,7 +2148,7 @@
         <v>10.67</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -1576,7 +2156,7 @@
         <v>10.42</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -1584,15 +2164,15 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>71</v>
       </c>
       <c r="B71">
-        <v>8.7260000000000009</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.726</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -1600,15 +2180,15 @@
         <v>11.14</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>73</v>
       </c>
       <c r="B73">
-        <v>9.3439999999999994</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.344</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -1616,15 +2196,15 @@
         <v>10.34</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>75</v>
       </c>
       <c r="B75">
-        <v>16.600000000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>16.6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -1632,23 +2212,23 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2">
       <c r="A77" t="s">
         <v>77</v>
       </c>
       <c r="B77">
-        <v>17.989999999999998</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
       <c r="B78">
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>17.6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -1656,23 +2236,23 @@
         <v>17.91</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2">
       <c r="A80" t="s">
         <v>80</v>
       </c>
       <c r="B80">
-        <v>9.5619999999999994</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>9.562</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" t="s">
         <v>81</v>
       </c>
       <c r="B81">
-        <v>5.9210000000000003</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5.921</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -1680,7 +2260,7 @@
         <v>347.3</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -1688,7 +2268,7 @@
         <v>384.5</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -1696,7 +2276,7 @@
         <v>15.04</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -1704,7 +2284,7 @@
         <v>26.12</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -1712,7 +2292,7 @@
         <v>24.06</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -1720,7 +2300,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -1728,7 +2308,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -1736,7 +2316,7 @@
         <v>20.3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -1744,7 +2324,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -1752,7 +2332,7 @@
         <v>13.36</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -1760,7 +2340,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -1768,7 +2348,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -1776,7 +2356,7 @@
         <v>12.07</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -1784,7 +2364,7 @@
         <v>12.32</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -1792,7 +2372,7 @@
         <v>11.7385555555556</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -1800,7 +2380,7 @@
         <v>10.52</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -1808,7 +2388,7 @@
         <v>10.77525</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -1816,7 +2396,7 @@
         <v>12.03</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -1824,7 +2404,7 @@
         <v>11.59</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -1832,7 +2412,7 @@
         <v>13.67</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -1840,7 +2420,7 @@
         <v>15.93</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -1848,7 +2428,7 @@
         <v>14.46</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -1856,7 +2436,7 @@
         <v>14.5845</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -1864,7 +2444,7 @@
         <v>14.09</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -1872,15 +2452,15 @@
         <v>15.66</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2">
       <c r="A107" t="s">
         <v>107</v>
       </c>
       <c r="B107">
-        <v>7.9516666666666698</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.95166666666667</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -1888,7 +2468,7 @@
         <v>14.05</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -1896,7 +2476,7 @@
         <v>18.68</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -1904,7 +2484,7 @@
         <v>14.32</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -1912,7 +2492,7 @@
         <v>12.17</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -1920,7 +2500,7 @@
         <v>12.84</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -1928,7 +2508,7 @@
         <v>14.33</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -1936,15 +2516,15 @@
         <v>11.24</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2">
       <c r="A115" t="s">
         <v>115</v>
       </c>
       <c r="B115">
-        <v>7.5397499999999997</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.53975</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -1952,7 +2532,7 @@
         <v>12.2445</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -1960,7 +2540,7 @@
         <v>11.39</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -1968,7 +2548,7 @@
         <v>12.51</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -1976,7 +2556,7 @@
         <v>12.06</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -1984,39 +2564,39 @@
         <v>11.95</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2">
       <c r="A121" t="s">
         <v>121</v>
       </c>
       <c r="B121">
-        <v>8.9369999999999994</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8.937</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
       <c r="A122" t="s">
         <v>122</v>
       </c>
       <c r="B122">
-        <v>7.7560000000000002</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.756</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
       <c r="A123" t="s">
         <v>123</v>
       </c>
       <c r="B123">
-        <v>7.8789999999999996</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.879</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
       <c r="A124" t="s">
         <v>124</v>
       </c>
       <c r="B124">
-        <v>7.5270000000000001</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.527</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -2024,7 +2604,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -2032,31 +2612,31 @@
         <v>10.63</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2">
       <c r="A127" t="s">
         <v>127</v>
       </c>
       <c r="B127">
-        <v>3.7440000000000002</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.744</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
       <c r="A128" t="s">
         <v>128</v>
       </c>
       <c r="B128">
-        <v>4.8449999999999998</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4.845</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
       <c r="A129" t="s">
         <v>129</v>
       </c>
       <c r="B129">
-        <v>4.6779999999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4.678</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
       <c r="A130" t="s">
         <v>130</v>
       </c>
@@ -2064,7 +2644,7 @@
         <v>27.78</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -2072,7 +2652,7 @@
         <v>17.87</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -2080,7 +2660,7 @@
         <v>21.31</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2">
       <c r="A133" t="s">
         <v>133</v>
       </c>
@@ -2088,7 +2668,7 @@
         <v>49.88</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -2096,7 +2676,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -2104,7 +2684,7 @@
         <v>20.37</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -2112,7 +2692,7 @@
         <v>24.7</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2">
       <c r="A137" t="s">
         <v>137</v>
       </c>
@@ -2120,7 +2700,7 @@
         <v>21.18</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -2128,7 +2708,7 @@
         <v>23.11</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -2136,7 +2716,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -2144,15 +2724,15 @@
         <v>20.37</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2">
       <c r="A141" t="s">
         <v>141</v>
       </c>
       <c r="B141">
-        <v>7.5759999999999996</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7.576</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
       <c r="A142" t="s">
         <v>142</v>
       </c>
@@ -2160,7 +2740,7 @@
         <v>17.8</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -2168,7 +2748,7 @@
         <v>22.43</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -2176,7 +2756,7 @@
         <v>18.37</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2">
       <c r="A145" t="s">
         <v>145</v>
       </c>
@@ -2184,7 +2764,7 @@
         <v>17.29</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2">
       <c r="A146" t="s">
         <v>146</v>
       </c>
@@ -2192,7 +2772,7 @@
         <v>16.62</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -2200,7 +2780,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -2208,7 +2788,7 @@
         <v>14.55</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2">
       <c r="A149" t="s">
         <v>149</v>
       </c>
@@ -2216,7 +2796,7 @@
         <v>15.48</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -2224,23 +2804,23 @@
         <v>23.13</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2">
       <c r="A151" t="s">
         <v>151</v>
       </c>
       <c r="B151">
-        <v>18.489999999999998</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+        <v>18.49</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
       <c r="A152" t="s">
         <v>152</v>
       </c>
       <c r="B152">
-        <v>2.1240000000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2.124</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
       <c r="A153" t="s">
         <v>153</v>
       </c>
@@ -2248,7 +2828,7 @@
         <v>12.29</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -2256,7 +2836,7 @@
         <v>20.43</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2">
       <c r="A155" t="s">
         <v>155</v>
       </c>
@@ -2264,15 +2844,15 @@
         <v>7.86</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2">
       <c r="A156" t="s">
         <v>156</v>
       </c>
       <c r="B156">
-        <v>5.5039999999999996</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5.504</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
       <c r="A157" t="s">
         <v>157</v>
       </c>
@@ -2280,15 +2860,15 @@
         <v>14.88</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2">
       <c r="A158" t="s">
         <v>158</v>
       </c>
       <c r="B158">
-        <v>3.4790000000000001</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3.479</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
       <c r="A159" t="s">
         <v>159</v>
       </c>
@@ -2296,7 +2876,7 @@
         <v>13.96</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -2304,23 +2884,23 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2">
       <c r="A161" t="s">
         <v>161</v>
       </c>
       <c r="B161">
-        <v>4.5979999999999999</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4.598</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
       <c r="A162" t="s">
         <v>162</v>
       </c>
       <c r="B162">
-        <v>64.959999999999994</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+        <v>64.96</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
       <c r="A163" t="s">
         <v>163</v>
       </c>
@@ -2328,15 +2908,15 @@
         <v>27.8599999999999</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2">
       <c r="A164" t="s">
         <v>164</v>
       </c>
       <c r="B164">
-        <v>24.696000000000002</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+        <v>24.696</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
       <c r="A165" t="s">
         <v>165</v>
       </c>
@@ -2344,31 +2924,31 @@
         <v>24.2</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2">
       <c r="A166" t="s">
         <v>166</v>
       </c>
       <c r="B166">
-        <v>23.335999999999999</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23.336</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
       <c r="A167" t="s">
         <v>167</v>
       </c>
       <c r="B167">
-        <v>28.623999999999999</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+        <v>28.624</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
       <c r="A168" t="s">
         <v>168</v>
       </c>
       <c r="B168">
-        <v>23.748000000000001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23.748</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
       <c r="A169" t="s">
         <v>169</v>
       </c>
@@ -2376,7 +2956,7 @@
         <v>23.916</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -2384,7 +2964,7 @@
         <v>25.24</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2">
       <c r="A171" t="s">
         <v>171</v>
       </c>
@@ -2392,31 +2972,31 @@
         <v>23.872</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2">
       <c r="A172" t="s">
         <v>172</v>
       </c>
       <c r="B172">
-        <v>24.344000000000001</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+        <v>24.344</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
       <c r="A173" t="s">
         <v>173</v>
       </c>
       <c r="B173">
-        <v>26.504000000000001</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26.504</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
       <c r="A174" t="s">
         <v>174</v>
       </c>
       <c r="B174">
-        <v>27.943999999999999</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27.944</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
       <c r="A175" t="s">
         <v>175</v>
       </c>
@@ -2424,15 +3004,15 @@
         <v>26.988</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2">
       <c r="A176" t="s">
         <v>176</v>
       </c>
       <c r="B176">
-        <v>27.007999999999999</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+        <v>27.008</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
       <c r="A177" t="s">
         <v>177</v>
       </c>
@@ -2440,7 +3020,7 @@
         <v>27.616</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2">
       <c r="A178" t="s">
         <v>178</v>
       </c>
@@ -2448,7 +3028,7 @@
         <v>27.256</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2">
       <c r="A179" t="s">
         <v>179</v>
       </c>
@@ -2456,15 +3036,15 @@
         <v>26.564</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2">
       <c r="A180" t="s">
         <v>180</v>
       </c>
       <c r="B180">
-        <v>23.431999999999999</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23.432</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
       <c r="A181" t="s">
         <v>181</v>
       </c>
@@ -2472,23 +3052,23 @@
         <v>23.72</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2">
       <c r="A182" t="s">
         <v>182</v>
       </c>
       <c r="B182">
-        <v>23.928000000000001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23.928</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
       <c r="A183" t="s">
         <v>183</v>
       </c>
       <c r="B183">
-        <v>23.463999999999999</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+        <v>23.464</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
       <c r="A184" t="s">
         <v>184</v>
       </c>
@@ -2496,7 +3076,7 @@
         <v>23.08</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2">
       <c r="A185" t="s">
         <v>185</v>
       </c>
@@ -2504,7 +3084,7 @@
         <v>23.78</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2">
       <c r="A186" t="s">
         <v>186</v>
       </c>
@@ -2512,7 +3092,7 @@
         <v>23.1</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2">
       <c r="A187" t="s">
         <v>187</v>
       </c>
@@ -2520,7 +3100,7 @@
         <v>23.584</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -2528,7 +3108,7 @@
         <v>24.404</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2">
       <c r="A189" t="s">
         <v>189</v>
       </c>
@@ -2536,191 +3116,32 @@
         <v>25.82</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2">
       <c r="A190" t="s">
         <v>190</v>
       </c>
       <c r="B190">
-        <v>26.568000000000001</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26.568</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
       <c r="A191" t="s">
         <v>191</v>
       </c>
       <c r="B191">
-        <v>26.588000000000001</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+        <v>26.588</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
       <c r="A192" t="s">
         <v>192</v>
       </c>
       <c r="B192">
-        <v>25.684000000000001</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>193</v>
-      </c>
-      <c r="B193">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>194</v>
-      </c>
-      <c r="B194">
-        <v>1.7609999999999999</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>195</v>
-      </c>
-      <c r="B195">
-        <v>0.94429689999999999</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>196</v>
-      </c>
-      <c r="B196">
-        <v>2.218</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>197</v>
-      </c>
-      <c r="B197">
-        <v>0.94799999999999995</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>198</v>
-      </c>
-      <c r="B198">
-        <v>1.2549999999999999</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>199</v>
-      </c>
-      <c r="B199">
-        <v>0.96689999999999998</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>200</v>
-      </c>
-      <c r="B200">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>201</v>
-      </c>
-      <c r="B201">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>202</v>
-      </c>
-      <c r="B202">
-        <v>1.909</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>203</v>
-      </c>
-      <c r="B203">
-        <v>1.968</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>204</v>
-      </c>
-      <c r="B204">
-        <v>4.2409999999999997</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>205</v>
-      </c>
-      <c r="B205">
-        <v>0.83055718000000001</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>206</v>
-      </c>
-      <c r="B206">
-        <v>2.923</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>207</v>
-      </c>
-      <c r="B207">
-        <v>2.3358287</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>208</v>
-      </c>
-      <c r="B208">
-        <v>1.9690000000000001</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>209</v>
-      </c>
-      <c r="B209">
-        <v>69.260000000000005</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>210</v>
-      </c>
-      <c r="B210">
-        <v>2.302</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>211</v>
-      </c>
-      <c r="B211">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>212</v>
-      </c>
-      <c r="B212">
-        <v>1.9019999999999999</v>
+        <v>25.684</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>